--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260624.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260624.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>133,741,000</t>
+          <t>133,095,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>15.75%</t>
+          <t>16.47%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>3,194,000</t>
+          <t>3,186,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.03%</t>
+          <t>9.49%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>1,752,000</t>
+          <t>1,743,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.07%</t>
+          <t>5.94%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>10,913,000</t>
+          <t>10,790,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.93%</t>
+          <t>5.78%</t>
         </is>
       </c>
     </row>
@@ -699,56 +699,56 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>21,875,000</t>
+          <t>21,621,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.21%</t>
+          <t>5.08%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>環球晶圓</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>5,967,000</t>
+          <t>4,712,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>4.11%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>環球晶圓</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>4,770,000</t>
+          <t>5,967,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.16%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
@@ -809,73 +809,73 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>19,329,000</t>
+          <t>19,135,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.66%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>8,655,000</t>
+          <t>2,793,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2,793,000</t>
+          <t>8,655,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>15,094,000</t>
+          <t>14,170,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,22 +887,22 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>14,170,000</t>
+          <t>15,094,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>66,656,000</t>
+          <t>62,420,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1034,73 +1034,73 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>宏碁股份</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>19,628,000</t>
+          <t>61,597,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>宏碁股份</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>61,597,000</t>
+          <t>19,628,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>和碩聯合</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2,027,877,264</t>
+          <t>23,330,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
@@ -1122,29 +1122,29 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>和碩聯合</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>23,330,000</t>
+          <t>1,856,764,663</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1232,73 +1232,73 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>14,421,000</t>
+          <t>14,278,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,846,000</t>
+          <t>14,421,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>14,278,000</t>
+          <t>1,846,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>992,518,378</t>
+          <t>959,558,378</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-629,631,891</t>
+          <t>-537,211,840</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-0.37%</t>
         </is>
       </c>
     </row>
